--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.02053784441594242</v>
       </c>
       <c r="C2" t="n">
-        <v>105617124</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>105617124</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>71742341</v>
+        <v>4200450</v>
       </c>
       <c r="L2" t="n">
-        <v>40631895</v>
+        <v>2331449</v>
       </c>
       <c r="M2" t="n">
-        <v>10115716</v>
+        <v>569968</v>
       </c>
       <c r="N2" t="n">
-        <v>548071</v>
+        <v>27386</v>
       </c>
       <c r="O2" t="n">
-        <v>6116081</v>
+        <v>354195</v>
       </c>
       <c r="P2" t="n">
-        <v>2504940</v>
+        <v>148358</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999185800552368</v>
+        <v>0.9999269247055054</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8603891730308533</v>
+        <v>0.8563995957374573</v>
       </c>
       <c r="S2" t="n">
-        <v>0.731850266456604</v>
+        <v>0.7134827375411987</v>
       </c>
       <c r="T2" t="n">
-        <v>0.649570643901825</v>
+        <v>0.6232850551605225</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4739704728126526</v>
+        <v>0.4036256372928619</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7059028744697571</v>
+        <v>0.6948569416999817</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7649577856063843</v>
+        <v>0.7700988054275513</v>
       </c>
       <c r="X2" t="n">
-        <v>105617124</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>105617124</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>69938062</v>
+        <v>4098451</v>
       </c>
       <c r="AG2" t="n">
-        <v>37621777</v>
+        <v>2160035</v>
       </c>
       <c r="AH2" t="n">
-        <v>9196688</v>
+        <v>523313</v>
       </c>
       <c r="AI2" t="n">
-        <v>507268</v>
+        <v>26078</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5626603</v>
+        <v>326935</v>
       </c>
       <c r="AK2" t="n">
-        <v>2357052</v>
+        <v>139695</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8331757783889771</v>
+        <v>0.8300260305404663</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6906946301460266</v>
+        <v>0.6741499304771423</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5841453075408936</v>
+        <v>0.565066933631897</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3376325964927673</v>
+        <v>0.2950734198093414</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6514595746994019</v>
+        <v>0.6435044407844543</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7174167633056641</v>
+        <v>0.7228233218193054</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.005246048466141522</v>
       </c>
       <c r="C3" t="n">
-        <v>2649</v>
+        <v>112</v>
       </c>
       <c r="D3" t="n">
-        <v>71742341</v>
+        <v>4200450</v>
       </c>
       <c r="E3" t="n">
-        <v>10586394</v>
+        <v>664697</v>
       </c>
       <c r="F3" t="n">
-        <v>585435</v>
+        <v>24633</v>
       </c>
       <c r="G3" t="n">
-        <v>72854</v>
+        <v>4249</v>
       </c>
       <c r="H3" t="n">
-        <v>56100</v>
+        <v>1084</v>
       </c>
       <c r="I3" t="n">
-        <v>9203</v>
+        <v>102</v>
       </c>
       <c r="J3" t="n">
-        <v>167571077</v>
+        <v>9857174</v>
       </c>
       <c r="K3" t="n">
-        <v>178500573</v>
+        <v>10470745</v>
       </c>
       <c r="L3" t="n">
-        <v>203109509</v>
+        <v>11894941</v>
       </c>
       <c r="M3" t="n">
-        <v>251881895</v>
+        <v>14794405</v>
       </c>
       <c r="N3" t="n">
-        <v>271077706</v>
+        <v>15941176</v>
       </c>
       <c r="O3" t="n">
-        <v>261981460</v>
+        <v>15405420</v>
       </c>
       <c r="P3" t="n">
-        <v>269137948</v>
+        <v>15832717</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8637934327125549</v>
+        <v>0.8580529689788818</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7360880374908447</v>
+        <v>0.7197594046592712</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6379058361053467</v>
+        <v>0.6118786334991455</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3627627193927765</v>
+        <v>0.3085398972034454</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7056561708450317</v>
+        <v>0.6952674984931946</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7615697383880615</v>
+        <v>0.7671322226524353</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>69938062</v>
+        <v>4098451</v>
       </c>
       <c r="Z3" t="n">
-        <v>11964837</v>
+        <v>740530</v>
       </c>
       <c r="AA3" t="n">
-        <v>813648</v>
+        <v>38881</v>
       </c>
       <c r="AB3" t="n">
-        <v>250004</v>
+        <v>15351</v>
       </c>
       <c r="AC3" t="n">
-        <v>74952</v>
+        <v>1917</v>
       </c>
       <c r="AD3" t="n">
-        <v>13473</v>
+        <v>197</v>
       </c>
       <c r="AE3" t="n">
-        <v>167579676</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>176138340</v>
+        <v>10335786</v>
       </c>
       <c r="AG3" t="n">
-        <v>201149322</v>
+        <v>11787142</v>
       </c>
       <c r="AH3" t="n">
-        <v>250791958</v>
+        <v>14736100</v>
       </c>
       <c r="AI3" t="n">
-        <v>270690817</v>
+        <v>15919340</v>
       </c>
       <c r="AJ3" t="n">
-        <v>261519260</v>
+        <v>15379844</v>
       </c>
       <c r="AK3" t="n">
-        <v>268979201</v>
+        <v>15823439</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8420695066452026</v>
+        <v>0.8372169733047485</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6815567016601562</v>
+        <v>0.6668409109115601</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5799511671066284</v>
+        <v>0.5617930293083191</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3357556164264679</v>
+        <v>0.2938035130500793</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.649181604385376</v>
+        <v>0.6417574882507324</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7166078090667725</v>
+        <v>0.7223374247550964</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.05517314881591997</v>
       </c>
       <c r="C4" t="n">
-        <v>1023</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
-        <v>10773326</v>
+        <v>669109</v>
       </c>
       <c r="E4" t="n">
-        <v>40631895</v>
+        <v>2331449</v>
       </c>
       <c r="F4" t="n">
-        <v>3130694</v>
+        <v>207929</v>
       </c>
       <c r="G4" t="n">
-        <v>128055</v>
+        <v>7588</v>
       </c>
       <c r="H4" t="n">
-        <v>465461</v>
+        <v>20964</v>
       </c>
       <c r="I4" t="n">
-        <v>69322</v>
+        <v>2126</v>
       </c>
       <c r="J4" t="n">
-        <v>8599</v>
+        <v>454</v>
       </c>
       <c r="K4" t="n">
-        <v>11641251</v>
+        <v>704328</v>
       </c>
       <c r="L4" t="n">
-        <v>14887515</v>
+        <v>936253</v>
       </c>
       <c r="M4" t="n">
-        <v>5457211</v>
+        <v>344490</v>
       </c>
       <c r="N4" t="n">
-        <v>608269</v>
+        <v>40464</v>
       </c>
       <c r="O4" t="n">
-        <v>2548115</v>
+        <v>155543</v>
       </c>
       <c r="P4" t="n">
-        <v>769672</v>
+        <v>44290</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999592900276184</v>
+        <v>0.9999634623527527</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8620879650115967</v>
+        <v>0.8572255373001099</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7339630722999573</v>
+        <v>0.716607391834259</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6436853408813477</v>
+        <v>0.6175291538238525</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4109764397144318</v>
+        <v>0.3497350215911865</v>
       </c>
       <c r="V4" t="n">
-        <v>0.705779492855072</v>
+        <v>0.6950621604919434</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7632600069046021</v>
+        <v>0.7686126828193665</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>12901572</v>
+        <v>792041</v>
       </c>
       <c r="Z4" t="n">
-        <v>37621777</v>
+        <v>2160035</v>
       </c>
       <c r="AA4" t="n">
-        <v>3754828</v>
+        <v>238897</v>
       </c>
       <c r="AB4" t="n">
-        <v>254205</v>
+        <v>15541</v>
       </c>
       <c r="AC4" t="n">
-        <v>577179</v>
+        <v>29154</v>
       </c>
       <c r="AD4" t="n">
-        <v>90215</v>
+        <v>3538</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>14003484</v>
+        <v>839287</v>
       </c>
       <c r="AG4" t="n">
-        <v>16847702</v>
+        <v>1044052</v>
       </c>
       <c r="AH4" t="n">
-        <v>6547148</v>
+        <v>402795</v>
       </c>
       <c r="AI4" t="n">
-        <v>995158</v>
+        <v>62300</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3010315</v>
+        <v>181119</v>
       </c>
       <c r="AK4" t="n">
-        <v>928419</v>
+        <v>53568</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8375990390777588</v>
+        <v>0.8336060047149658</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6860952973365784</v>
+        <v>0.6704755425453186</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5820406675338745</v>
+        <v>0.5634252429008484</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3366914987564087</v>
+        <v>0.2944370806217194</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6503186225891113</v>
+        <v>0.6426298022270203</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7170120477676392</v>
+        <v>0.7225802540779114</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1609</v>
+        <v>85</v>
       </c>
       <c r="D5" t="n">
-        <v>609832</v>
+        <v>22616</v>
       </c>
       <c r="E5" t="n">
-        <v>3473705</v>
+        <v>231466</v>
       </c>
       <c r="F5" t="n">
-        <v>10115716</v>
+        <v>569968</v>
       </c>
       <c r="G5" t="n">
-        <v>222562</v>
+        <v>15667</v>
       </c>
       <c r="H5" t="n">
-        <v>1263782</v>
+        <v>83321</v>
       </c>
       <c r="I5" t="n">
-        <v>170488</v>
+        <v>8382</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11312635</v>
+        <v>694877</v>
       </c>
       <c r="L5" t="n">
-        <v>14567881</v>
+        <v>907757</v>
       </c>
       <c r="M5" t="n">
-        <v>5741978</v>
+        <v>361537</v>
       </c>
       <c r="N5" t="n">
-        <v>962754</v>
+        <v>61374</v>
       </c>
       <c r="O5" t="n">
-        <v>2551144</v>
+        <v>155242</v>
       </c>
       <c r="P5" t="n">
-        <v>784240</v>
+        <v>45035</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999685287475586</v>
+        <v>0.9999717473983765</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9159803986549377</v>
+        <v>0.9129327535629272</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8921825289726257</v>
+        <v>0.8852542638778687</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9590069055557251</v>
+        <v>0.9560666084289551</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9942494630813599</v>
+        <v>0.9936630129814148</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9813348650932312</v>
+        <v>0.9806610345840454</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9943121075630188</v>
+        <v>0.9944416284561157</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>777471</v>
+        <v>32315</v>
       </c>
       <c r="Z5" t="n">
-        <v>3914144</v>
+        <v>252709</v>
       </c>
       <c r="AA5" t="n">
-        <v>9196688</v>
+        <v>523313</v>
       </c>
       <c r="AB5" t="n">
-        <v>275265</v>
+        <v>17597</v>
       </c>
       <c r="AC5" t="n">
-        <v>1482848</v>
+        <v>94225</v>
       </c>
       <c r="AD5" t="n">
-        <v>211278</v>
+        <v>11346</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>13116914</v>
+        <v>796876</v>
       </c>
       <c r="AG5" t="n">
-        <v>17577999</v>
+        <v>1079171</v>
       </c>
       <c r="AH5" t="n">
-        <v>6661006</v>
+        <v>408192</v>
       </c>
       <c r="AI5" t="n">
-        <v>1003557</v>
+        <v>62682</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3040622</v>
+        <v>182502</v>
       </c>
       <c r="AK5" t="n">
-        <v>932128</v>
+        <v>53698</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9007294178009033</v>
+        <v>0.8981877565383911</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8739893436431885</v>
+        <v>0.8678798675537109</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9516533613204956</v>
+        <v>0.9495353698730469</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9926839470863342</v>
+        <v>0.9922228455543518</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.977851390838623</v>
+        <v>0.9773732423782349</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9931896924972534</v>
+        <v>0.9933252334594727</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>2251</v>
+        <v>156</v>
       </c>
       <c r="D6" t="n">
-        <v>190976</v>
+        <v>12233</v>
       </c>
       <c r="E6" t="n">
-        <v>265972</v>
+        <v>17040</v>
       </c>
       <c r="F6" t="n">
-        <v>305117</v>
+        <v>18577</v>
       </c>
       <c r="G6" t="n">
-        <v>548071</v>
+        <v>27386</v>
       </c>
       <c r="H6" t="n">
-        <v>169718</v>
+        <v>11628</v>
       </c>
       <c r="I6" t="n">
-        <v>28720</v>
+        <v>1740</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>228660</v>
+        <v>13580</v>
       </c>
       <c r="Z6" t="n">
-        <v>266944</v>
+        <v>16627</v>
       </c>
       <c r="AA6" t="n">
-        <v>284975</v>
+        <v>18486</v>
       </c>
       <c r="AB6" t="n">
-        <v>507268</v>
+        <v>26078</v>
       </c>
       <c r="AC6" t="n">
-        <v>189359</v>
+        <v>11941</v>
       </c>
       <c r="AD6" t="n">
-        <v>33619</v>
+        <v>2048</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>668</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>62395</v>
+        <v>321</v>
       </c>
       <c r="E7" t="n">
-        <v>508551</v>
+        <v>21902</v>
       </c>
       <c r="F7" t="n">
-        <v>1324532</v>
+        <v>89122</v>
       </c>
       <c r="G7" t="n">
-        <v>163059</v>
+        <v>11924</v>
       </c>
       <c r="H7" t="n">
-        <v>6116081</v>
+        <v>354195</v>
       </c>
       <c r="I7" t="n">
-        <v>491939</v>
+        <v>31940</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>87891</v>
+        <v>1284</v>
       </c>
       <c r="Z7" t="n">
-        <v>633637</v>
+        <v>31973</v>
       </c>
       <c r="AA7" t="n">
-        <v>1551057</v>
+        <v>100506</v>
       </c>
       <c r="AB7" t="n">
-        <v>188203</v>
+        <v>12300</v>
       </c>
       <c r="AC7" t="n">
-        <v>5626603</v>
+        <v>326935</v>
       </c>
       <c r="AD7" t="n">
-        <v>579834</v>
+        <v>36439</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>399</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>4722</v>
+        <v>49</v>
       </c>
       <c r="E8" t="n">
-        <v>52893</v>
+        <v>1148</v>
       </c>
       <c r="F8" t="n">
-        <v>111433</v>
+        <v>4229</v>
       </c>
       <c r="G8" t="n">
-        <v>21739</v>
+        <v>1036</v>
       </c>
       <c r="H8" t="n">
-        <v>593054</v>
+        <v>38546</v>
       </c>
       <c r="I8" t="n">
-        <v>2504940</v>
+        <v>148358</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>7890</v>
+        <v>67</v>
       </c>
       <c r="Z8" t="n">
-        <v>68140</v>
+        <v>2213</v>
       </c>
       <c r="AA8" t="n">
-        <v>142640</v>
+        <v>6025</v>
       </c>
       <c r="AB8" t="n">
-        <v>27481</v>
+        <v>1511</v>
       </c>
       <c r="AC8" t="n">
-        <v>685977</v>
+        <v>43882</v>
       </c>
       <c r="AD8" t="n">
-        <v>2357052</v>
+        <v>139695</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
